--- a/Tests/Brace and Plate measurements.xlsx
+++ b/Tests/Brace and Plate measurements.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dws/Library/CloudStorage/Dropbox/Programming/src/GuitarTap/Tests/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dws/src/GuitarTap/Tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D564A21C-0FA7-A746-B686-85CE75705456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B092F7-DFE4-D943-BA9C-625846B417E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="820" yWindow="3320" windowWidth="28040" windowHeight="17180" xr2:uid="{67472550-BA94-354C-9432-C4165406051B}"/>
+    <workbookView xWindow="820" yWindow="2880" windowWidth="28040" windowHeight="17180" xr2:uid="{67472550-BA94-354C-9432-C4165406051B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="11">
   <si>
     <t>Width</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>gm/cm^3</t>
+  </si>
+  <si>
+    <t>Bout Width</t>
   </si>
 </sst>
 </file>
@@ -95,7 +98,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -118,16 +121,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFA3A3A3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFA3A3A3"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -507,7 +527,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>0.48499999999999999</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
@@ -530,9 +550,35 @@
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="B6" s="1">
+        <v>0.34889999999999999</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="4">
+        <v>490</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="4">
+        <v>368</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">

--- a/Tests/Brace and Plate measurements.xlsx
+++ b/Tests/Brace and Plate measurements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dws/src/GuitarTap/Tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B092F7-DFE4-D943-BA9C-625846B417E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6491CC-C846-3E48-89A6-AEC338E4943C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="820" yWindow="2880" windowWidth="28040" windowHeight="17180" xr2:uid="{67472550-BA94-354C-9432-C4165406051B}"/>
+    <workbookView xWindow="820" yWindow="1260" windowWidth="28040" windowHeight="17180" xr2:uid="{67472550-BA94-354C-9432-C4165406051B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -122,21 +122,38 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFA3A3A3"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color rgb="FFA3A3A3"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="medium">
+        <color rgb="FFA3A3A3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFA3A3A3"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -144,10 +161,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -493,90 +513,90 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="5">
         <v>220.5</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1">
+      <c r="C2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
         <f>B2*0.224</f>
         <v>49.392000000000003</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="5">
         <v>557.5</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="C3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
         <f>B3*0.224</f>
         <v>124.88000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="5">
         <v>4.8499999999999996</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1"/>
+      <c r="C4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="5">
         <v>208</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="1"/>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="4">
         <v>0.34889999999999999</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="5">
         <v>490</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="C7" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <v>368</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="4" t="s">
         <v>1</v>
       </c>
     </row>
